--- a/tumores/8. Seno paranasal y cavidad nasal.xlsx
+++ b/tumores/8. Seno paranasal y cavidad nasal.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\Proyecto Practicas\tumores\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64591A59-353E-447D-A47E-150BB807D59A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34D00A0-F3DC-46EF-B44F-A368E0DEEA5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1116" yWindow="1116" windowWidth="8520" windowHeight="8880" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
   <sheets>
     <sheet name="TNM" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="103">
   <si>
     <t>T</t>
   </si>
@@ -112,36 +112,12 @@
     <t>IVB</t>
   </si>
   <si>
-    <t>Bilateral retrofaringea &lt;6cm, encima del cricoides</t>
-  </si>
-  <si>
-    <t>Unilateral retrofaringea &lt;6cm, encima del cricoides</t>
-  </si>
-  <si>
-    <t>Unilateral cervical &lt;6cm</t>
-  </si>
-  <si>
-    <t>Unilateral cervical &lt;6cm, encima del cricoides</t>
-  </si>
-  <si>
-    <t>Unilateral cervical &gt;6cm</t>
-  </si>
-  <si>
-    <t>Bilateral cervical &gt;6cm</t>
-  </si>
-  <si>
-    <t>Debajo del cricoides</t>
-  </si>
-  <si>
     <t>T1, T2</t>
   </si>
   <si>
     <t>Seno maxilar</t>
   </si>
   <si>
-    <t>Hueso de pared post. seno max., Tejido subcutáneo, Piso o pared medio de la órbita, Fosa pterigoidea, Seno etmoidal</t>
-  </si>
-  <si>
     <t>Contenido anterior de órbita, Piel de la mejilla, Placa pterigoidea, Fosa infratemporal, Lamina cribosa, Senos esfenoidales, Senos frontales</t>
   </si>
   <si>
@@ -157,39 +133,21 @@
     <t>Cavidad nasal y seno etmoidal</t>
   </si>
   <si>
-    <t>Diseminación</t>
-  </si>
-  <si>
-    <t>Piso de la orbita, Pared media de la orbita, Seno maxilar, Paladar, Lamina cribosa</t>
-  </si>
-  <si>
     <t>Contenido anterior de órbita, Piel de la mejilla, Piel de la nariz, Placa pterigoidea, Fosa infratemporal, Lamina cribosa, Senos esfenoidales, Senos frontales</t>
   </si>
   <si>
     <t>Restringido a cualquier subsitio</t>
   </si>
   <si>
-    <t>Invasion dos subsitios</t>
-  </si>
-  <si>
-    <t>Region en complejo nasoetmoidal</t>
-  </si>
-  <si>
     <t>N2a</t>
   </si>
   <si>
-    <t>Multiples ganglios ipsilateral ≤6 cm y ENE-</t>
-  </si>
-  <si>
     <t>N2b</t>
   </si>
   <si>
     <t>N2c</t>
   </si>
   <si>
-    <t>Un ganglio ipsilateral &gt;6 cm y ENE-</t>
-  </si>
-  <si>
     <t>N3a</t>
   </si>
   <si>
@@ -256,18 +214,12 @@
     <t>🟨 N2a: Un ganglio ipsilateral &gt;3 cm pero ≤6 cm y ENE-</t>
   </si>
   <si>
-    <t>🟨N2b: Multiples ganglios ipsilateral ≤6 cm y ENE-</t>
-  </si>
-  <si>
     <t>🟨N2c: Ganglios contralaterales ≤6 cm y ENE-</t>
   </si>
   <si>
     <t>🟨N2c: Ganglios bilaterales ≤6 cm y ENE-</t>
   </si>
   <si>
-    <t>🟦N3a: Un ganglio ipsilateral &gt;6 cm y ENE-</t>
-  </si>
-  <si>
     <t>🟦N3b: Uno o más ganglios con ENEc</t>
   </si>
   <si>
@@ -301,12 +253,6 @@
     <t>Ganglio ipsilat.</t>
   </si>
   <si>
-    <t>Contralaterales ≤6 cm y ENE-</t>
-  </si>
-  <si>
-    <t>Bilaterales ≤6 cm y ENE-</t>
-  </si>
-  <si>
     <t>🟦N3b: Uno o varios ganglios ENE+ *</t>
   </si>
   <si>
@@ -341,6 +287,54 @@
   </si>
   <si>
     <t xml:space="preserve">Inv: </t>
+  </si>
+  <si>
+    <t>Hueso de pared post. del seno max., Tejido subcutáneo, Suelo o pared medio de la órbita, Fosa pterigoidea, Seno etmoidal</t>
+  </si>
+  <si>
+    <t>Vértice orbitario, Duramadre, Encéfalo, Fosa craneal media, Pares craneales (no nv.trigémico), Nasofaringe, Clivus</t>
+  </si>
+  <si>
+    <t>Invasion dos subsitios en una región</t>
+  </si>
+  <si>
+    <t>Región en complejo nasoetmoidal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disem. </t>
+  </si>
+  <si>
+    <t>🟦N3a: Un ganglio &gt;6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Ganglio ipsilateral &gt;3 cm pero ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Múltiples ganglios ipsilateral ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>🟨N2b: Múltiples ganglios ipsilateral ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Ganglios contralaterales ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Ganglios bilaterales ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Un ganglio &gt;6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Ganglios con ENEc</t>
+  </si>
+  <si>
+    <t>G.Contralaterales ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>G.Bilaterales ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Suelo de la órbita, Pared media de la órbita, Seno maxilar, Paladar, Lamina cribosa</t>
   </si>
 </sst>
 </file>
@@ -946,10 +940,10 @@
         <v>7</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>8</v>
@@ -969,11 +963,11 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="1" t="s">
@@ -988,11 +982,11 @@
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
@@ -1007,18 +1001,18 @@
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
@@ -1026,18 +1020,18 @@
         <v>0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
@@ -1045,20 +1039,20 @@
         <v>0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="72" x14ac:dyDescent="0.3">
@@ -1066,20 +1060,20 @@
         <v>0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="10" customFormat="1" ht="72" x14ac:dyDescent="0.3">
@@ -1087,20 +1081,20 @@
         <v>0</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1108,11 +1102,11 @@
         <v>0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="5" t="s">
@@ -1127,11 +1121,11 @@
         <v>0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
@@ -1146,16 +1140,16 @@
         <v>0</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1163,16 +1157,16 @@
         <v>0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -1180,16 +1174,16 @@
         <v>0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1197,19 +1191,19 @@
         <v>0</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>44</v>
+        <v>102</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" ht="93" customHeight="1" x14ac:dyDescent="0.3">
@@ -1217,19 +1211,19 @@
         <v>0</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
@@ -1237,19 +1231,19 @@
         <v>0</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1266,10 +1260,10 @@
         <v>12</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5" t="s">
@@ -1284,10 +1278,10 @@
         <v>12</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5" t="s">
@@ -1302,17 +1296,17 @@
         <v>12</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -1320,17 +1314,17 @@
         <v>12</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>29</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -1338,17 +1332,17 @@
         <v>12</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -1356,17 +1350,17 @@
         <v>12</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>31</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1374,17 +1368,17 @@
         <v>12</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>32</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -1392,17 +1386,17 @@
         <v>12</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1411,17 +1405,17 @@
       </c>
       <c r="B26" s="9"/>
       <c r="C26" s="9" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="E26" s="13"/>
       <c r="F26" s="13" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -1430,10 +1424,10 @@
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="14" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
@@ -1449,10 +1443,10 @@
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="14" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2" t="s">
@@ -1468,17 +1462,17 @@
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="14" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1487,19 +1481,19 @@
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="14" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1508,17 +1502,17 @@
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="14" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1527,17 +1521,17 @@
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="14" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -1546,36 +1540,36 @@
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="14" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="14" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1584,19 +1578,19 @@
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="15" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -1604,7 +1598,7 @@
         <v>18</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>20</v>
@@ -1618,13 +1612,13 @@
         <v>18</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1681,7 +1675,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1700,7 +1694,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>15</v>
@@ -1717,7 +1711,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>20</v>
@@ -1728,10 +1722,10 @@
     </row>
     <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>20</v>
@@ -1742,10 +1736,10 @@
     </row>
     <row r="8" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>20</v>
@@ -1759,7 +1753,7 @@
         <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>20</v>
@@ -1770,7 +1764,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>26</v>
@@ -1790,10 +1784,10 @@
         <v>26</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/tumores/8. Seno paranasal y cavidad nasal.xlsx
+++ b/tumores/8. Seno paranasal y cavidad nasal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34D00A0-F3DC-46EF-B44F-A368E0DEEA5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D587EA2-9520-4875-91F7-2AD598D8B4B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="101">
   <si>
     <t>T</t>
   </si>
@@ -118,24 +118,15 @@
     <t>Seno maxilar</t>
   </si>
   <si>
-    <t>Contenido anterior de órbita, Piel de la mejilla, Placa pterigoidea, Fosa infratemporal, Lamina cribosa, Senos esfenoidales, Senos frontales</t>
-  </si>
-  <si>
     <t>T4a</t>
   </si>
   <si>
-    <t>Vértice orbitario, Duramadre, Encéfalo, Fosa craneal media, Pares craneales (no nv.trigémico), Nasofaringe o Clivus</t>
-  </si>
-  <si>
     <t>T4b</t>
   </si>
   <si>
     <t>Cavidad nasal y seno etmoidal</t>
   </si>
   <si>
-    <t>Contenido anterior de órbita, Piel de la mejilla, Piel de la nariz, Placa pterigoidea, Fosa infratemporal, Lamina cribosa, Senos esfenoidales, Senos frontales</t>
-  </si>
-  <si>
     <t>Restringido a cualquier subsitio</t>
   </si>
   <si>
@@ -172,12 +163,6 @@
     <t>🟩T1: Limitado a la mucosa del seno maxilar sin erosión/destrucción ósea</t>
   </si>
   <si>
-    <t>🟨T2: Erosión ósea y diseminación al paladar duro o meato nasal medio (sin llegar pared posterior del seno max. ni placas pterigoideas)</t>
-  </si>
-  <si>
-    <t>🟩T1: Restringido a cualquier subsitio (Con o sin invasion osea)</t>
-  </si>
-  <si>
     <t>🟨T2: Invasión de dos subsitios en una sola región</t>
   </si>
   <si>
@@ -187,12 +172,6 @@
     <t>🟦T3: Invasión *</t>
   </si>
   <si>
-    <t>🟥T4a: Invasión moderada *</t>
-  </si>
-  <si>
-    <t>🟥 T4b: Invasión avanzada *</t>
-  </si>
-  <si>
     <t>Inv:</t>
   </si>
   <si>
@@ -220,9 +199,6 @@
     <t>🟨N2c: Ganglios bilaterales ≤6 cm y ENE-</t>
   </si>
   <si>
-    <t>🟦N3b: Uno o más ganglios con ENEc</t>
-  </si>
-  <si>
     <t>M0: Sin metástasis a distancia</t>
   </si>
   <si>
@@ -286,15 +262,9 @@
     <t>🟦T3: Diseminación *</t>
   </si>
   <si>
-    <t xml:space="preserve">Inv: </t>
-  </si>
-  <si>
     <t>Hueso de pared post. del seno max., Tejido subcutáneo, Suelo o pared medio de la órbita, Fosa pterigoidea, Seno etmoidal</t>
   </si>
   <si>
-    <t>Vértice orbitario, Duramadre, Encéfalo, Fosa craneal media, Pares craneales (no nv.trigémico), Nasofaringe, Clivus</t>
-  </si>
-  <si>
     <t>Invasion dos subsitios en una región</t>
   </si>
   <si>
@@ -325,9 +295,6 @@
     <t>Un ganglio &gt;6 cm y ENE-</t>
   </si>
   <si>
-    <t>Ganglios con ENEc</t>
-  </si>
-  <si>
     <t>G.Contralaterales ≤6 cm y ENE-</t>
   </si>
   <si>
@@ -335,6 +302,33 @@
   </si>
   <si>
     <t>Suelo de la órbita, Pared media de la órbita, Seno maxilar, Paladar, Lamina cribosa</t>
+  </si>
+  <si>
+    <t>🟨T2: Erosión ósea y diseminación al paladar duro o meato nasal medio (sin llegar pared posterior del seno max. ni apófisis pterigoides)</t>
+  </si>
+  <si>
+    <t>🟥T4a: Enfermedad localmente avanzada *</t>
+  </si>
+  <si>
+    <t>🟥 T4b: Enfermedad localmente muy avanzada *</t>
+  </si>
+  <si>
+    <t>Invasión del contenido anterior de órbita, Invasión de la Piel de la mejilla, Invasión del Apófisis pterigoides, Invasión de la Fosa infratemporal, Invasión de la Lamina cribosa, Invasión de Senos esfenoidales, Invasión de Senos frontales</t>
+  </si>
+  <si>
+    <t>Invasión de Apex orbitario, Invasión de Duramadre, Invasión de Cerebro, Invasión de Fosa craneal media, Invasión de Pares craneales excepto V2, Nasofaringe, Clivus</t>
+  </si>
+  <si>
+    <t>Invasión del contenido anterior de órbita, Invasión de la Piel de la mejilla, Invasión de la Piel de la nariz Invasión del Apófisis pterigoides, Invasión de la Fosa infratemporal, Invasión de la Lamina cribosa, Invasión de Senos esfenoidales, Invasión de Senos frontales</t>
+  </si>
+  <si>
+    <t>🟩T1: Restringido a cualquier subsitio (Con o sin invasión ósea)</t>
+  </si>
+  <si>
+    <t>🟦N3b: Uno o más ganglios con ENE+</t>
+  </si>
+  <si>
+    <t>Ganglios con ENE+</t>
   </si>
 </sst>
 </file>
@@ -929,7 +923,7 @@
     <col min="1" max="1" width="9" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="14.88671875" style="5" customWidth="1"/>
     <col min="4" max="4" width="35.33203125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="27.88671875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="44.33203125" style="5" customWidth="1"/>
     <col min="6" max="6" width="27.21875" style="5" customWidth="1"/>
     <col min="7" max="7" width="38.44140625" style="5" customWidth="1"/>
     <col min="8" max="16384" width="11.5546875" style="5"/>
@@ -940,10 +934,10 @@
         <v>7</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>8</v>
@@ -967,7 +961,7 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="1" t="s">
@@ -986,7 +980,7 @@
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
@@ -1005,14 +999,14 @@
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
@@ -1024,14 +1018,14 @@
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
@@ -1043,16 +1037,16 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="72" x14ac:dyDescent="0.3">
@@ -1064,19 +1058,17 @@
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" s="10" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" s="10" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>0</v>
       </c>
@@ -1085,28 +1077,26 @@
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>55</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="G8" s="9"/>
     </row>
     <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="5" t="s">
@@ -1121,11 +1111,11 @@
         <v>0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
@@ -1140,16 +1130,16 @@
         <v>0</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1157,16 +1147,16 @@
         <v>0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -1174,16 +1164,16 @@
         <v>0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1191,19 +1181,19 @@
         <v>0</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" ht="93" customHeight="1" x14ac:dyDescent="0.3">
@@ -1211,19 +1201,16 @@
         <v>0</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
@@ -1231,19 +1218,16 @@
         <v>0</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>32</v>
+        <v>94</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>96</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>86</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1260,10 +1244,10 @@
         <v>12</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5" t="s">
@@ -1278,10 +1262,10 @@
         <v>12</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5" t="s">
@@ -1296,17 +1280,17 @@
         <v>12</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -1314,17 +1298,17 @@
         <v>12</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -1332,17 +1316,17 @@
         <v>12</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -1350,17 +1334,17 @@
         <v>12</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1368,17 +1352,17 @@
         <v>12</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -1386,17 +1370,17 @@
         <v>12</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1405,17 +1389,17 @@
       </c>
       <c r="B26" s="9"/>
       <c r="C26" s="9" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="E26" s="13"/>
       <c r="F26" s="13" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -1424,10 +1408,10 @@
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="14" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
@@ -1443,10 +1427,10 @@
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="14" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2" t="s">
@@ -1462,17 +1446,17 @@
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="14" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1481,19 +1465,19 @@
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="14" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1502,17 +1486,17 @@
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="14" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1521,17 +1505,17 @@
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="14" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -1540,17 +1524,17 @@
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="14" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -1559,17 +1543,17 @@
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="14" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1578,19 +1562,19 @@
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G35" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -1598,7 +1582,7 @@
         <v>18</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>20</v>
@@ -1612,13 +1596,13 @@
         <v>18</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1675,7 +1659,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1711,7 +1695,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>20</v>
@@ -1722,10 +1706,10 @@
     </row>
     <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>20</v>
@@ -1736,10 +1720,10 @@
     </row>
     <row r="8" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>20</v>
@@ -1753,7 +1737,7 @@
         <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>20</v>
@@ -1764,7 +1748,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>26</v>
@@ -1784,10 +1768,10 @@
         <v>26</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/tumores/8. Seno paranasal y cavidad nasal.xlsx
+++ b/tumores/8. Seno paranasal y cavidad nasal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D587EA2-9520-4875-91F7-2AD598D8B4B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F299BBBA-CA78-430E-9E36-7115683D5FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="102">
   <si>
     <t>T</t>
   </si>
@@ -319,9 +319,6 @@
     <t>Invasión de Apex orbitario, Invasión de Duramadre, Invasión de Cerebro, Invasión de Fosa craneal media, Invasión de Pares craneales excepto V2, Nasofaringe, Clivus</t>
   </si>
   <si>
-    <t>Invasión del contenido anterior de órbita, Invasión de la Piel de la mejilla, Invasión de la Piel de la nariz Invasión del Apófisis pterigoides, Invasión de la Fosa infratemporal, Invasión de la Lamina cribosa, Invasión de Senos esfenoidales, Invasión de Senos frontales</t>
-  </si>
-  <si>
     <t>🟩T1: Restringido a cualquier subsitio (Con o sin invasión ósea)</t>
   </si>
   <si>
@@ -329,6 +326,12 @@
   </si>
   <si>
     <t>Ganglios con ENE+</t>
+  </si>
+  <si>
+    <t>Invasión del contenido anterior de órbita, Invasión de la piel de la mejilla, Invasión de la piel de la nariz, Invasión del apófisis pterigoides, Invasión de la fosa infratemporal, Invasión de la lamina cribosa, Invasión de senos esfenoidales, Invasión de senos frontales</t>
+  </si>
+  <si>
+    <t>Invasión de apex orbitario, Invasión de duramadre, Invasión de cerebro, Invasión de fosa craneal media, Invasión de pares craneales excepto V2, Invasión de nasofaringe, Invasión de clivus</t>
   </si>
 </sst>
 </file>
@@ -1028,7 +1031,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
@@ -1133,7 +1136,7 @@
         <v>32</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>3</v>
@@ -1207,7 +1210,7 @@
         <v>93</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>30</v>
@@ -1224,7 +1227,7 @@
         <v>94</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>31</v>
@@ -1392,14 +1395,14 @@
         <v>60</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E26" s="13"/>
       <c r="F26" s="13" t="s">
         <v>38</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -1459,7 +1462,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>12</v>
       </c>
@@ -1556,7 +1559,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
         <v>12</v>
       </c>

--- a/tumores/8. Seno paranasal y cavidad nasal.xlsx
+++ b/tumores/8. Seno paranasal y cavidad nasal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F299BBBA-CA78-430E-9E36-7115683D5FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{612D972C-D1AA-4E11-BE60-456E37F0BC12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -313,12 +313,6 @@
     <t>🟥 T4b: Enfermedad localmente muy avanzada *</t>
   </si>
   <si>
-    <t>Invasión del contenido anterior de órbita, Invasión de la Piel de la mejilla, Invasión del Apófisis pterigoides, Invasión de la Fosa infratemporal, Invasión de la Lamina cribosa, Invasión de Senos esfenoidales, Invasión de Senos frontales</t>
-  </si>
-  <si>
-    <t>Invasión de Apex orbitario, Invasión de Duramadre, Invasión de Cerebro, Invasión de Fosa craneal media, Invasión de Pares craneales excepto V2, Nasofaringe, Clivus</t>
-  </si>
-  <si>
     <t>🟩T1: Restringido a cualquier subsitio (Con o sin invasión ósea)</t>
   </si>
   <si>
@@ -332,6 +326,12 @@
   </si>
   <si>
     <t>Invasión de apex orbitario, Invasión de duramadre, Invasión de cerebro, Invasión de fosa craneal media, Invasión de pares craneales excepto V2, Invasión de nasofaringe, Invasión de clivus</t>
+  </si>
+  <si>
+    <t>Invasión de Apex orbitario, Invasión de duramadre, Invasión de cerebro, Invasión de fosa craneal media, Invasión de pares craneales excepto V2, Invasión de nasofaringe, Invasión de clivus</t>
+  </si>
+  <si>
+    <t>Invasión del contenido anterior de órbita, Invasión de la piel de la mejilla, Invasión de apófisis pterigoides, Invasión de la fosa infratemporal, Invasión de la lamina cribosa, Invasión de senos esfenoidales, Invasión de senos frontales</t>
   </si>
 </sst>
 </file>
@@ -1064,7 +1064,7 @@
         <v>93</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>30</v>
@@ -1083,7 +1083,7 @@
         <v>94</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>31</v>
@@ -1136,7 +1136,7 @@
         <v>32</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>3</v>
@@ -1210,7 +1210,7 @@
         <v>93</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>30</v>
@@ -1227,7 +1227,7 @@
         <v>94</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>31</v>
@@ -1395,14 +1395,14 @@
         <v>60</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E26" s="13"/>
       <c r="F26" s="13" t="s">
         <v>38</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
